--- a/backtest_runs/20260410_193731/by_symbol/TICL/TICL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TICL/TICL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-763.0200000000021</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>103800.97</v>
@@ -955,7 +955,7 @@
         <v>-9110.710000000014</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>94690.25999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-1755.259999999992</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>92935</v>
@@ -1277,7 +1277,7 @@
         <v>-9022.790000000005</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>90970.92999999999</v>
@@ -1553,7 +1553,7 @@
         <v>-2279.639999999997</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>99995.29000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-4287.669999999991</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>97323.15000000001</v>
